--- a/jpcore-r4/feature/ImagingStudyTest/StructureDefinition-jp-medicationadministrationBase.xlsx
+++ b/jpcore-r4/feature/ImagingStudyTest/StructureDefinition-jp-medicationadministrationBase.xlsx
@@ -268,11 +268,11 @@
     <t>患者への薬剤投与記録</t>
   </si>
   <si>
-    <t>患者が薬剤を服用する、あるいは投与される事象を説明します。これは、錠剤を飲むだけだったり、長時間の点滴だったりすることがあります。関連するリソースは、この事象を許可された処方箋や、患者と医療従事者の具体的な出会いと結びつけます。</t>
+    <t>患者が薬剤を服用する、あるいは投与される事象を説明します。これは、錠剤を飲むだけだったり、長時間の点滴だったりすることがあります。関連するリソースは、この事象を許可された処方箋や、患者と医療従事者の具体的なEncounter（診察、受診、入退院など）と結びつけます。</t>
   </si>
   <si>
     <t>dom-2:もしリソースが他のリソースに含まれている場合、そのリソースにはネストされたリソースを含めてはなりません (moshi risōsu ga hoka no risōsu ni fukumarete iru baai, sono risōsu ni wa nesuto sareta risōsu o fukumete wa narimasen). {contained.contained.empty()}
-dom-3:もしリソースが他のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含まれるリソースに参照されるべきです。 {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:もしリソースが別のリソースの中に含まれる場合、meta.versionIdまたはmeta.lastUpdatedを持つべきではありません。 {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:「もしリソースが他のリソースに含まれている場合、セキュリティラベルを持つべきではありません。」 {contained.meta.security.empty()}dom-6:「資源は堅牢な管理のために物語を持つべきである。」 {text.`div`.exists()}</t>
+dom-3:もしリソースが他のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含まれるリソースに参照されるべきです。 {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:もしリソースが別のリソースの中に含まれる場合、meta.versionIdまたはmeta.lastUpdatedを持つべきではありません。 {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:もしリソースが他のリソースに含まれている場合、セキュリティラベルを持つべきではありません。 {contained.meta.security.empty()}dom-6:資源は堅牢な管理のために物語を持つべきである。 {text.`div`.exists()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -297,10 +297,10 @@
     <t>このアーティファクトの論理ID</t>
   </si>
   <si>
-    <t>「リソースのURLで使用される論理ID。一度割り当てられたら、この値は変更されません。」</t>
-  </si>
-  <si>
-    <t>「リソースにIDがないのは、作成操作を使用してサーバーに送信されているときだけです。」</t>
+    <t>リソースのURLで使用される論理ID。一度割り当てられたら、この値は変更されません。</t>
+  </si>
+  <si>
+    <t>リソースにIDがないのは、作成操作を使用してサーバーに送信されているときだけです。</t>
   </si>
   <si>
     <t>Resource.id</t>
@@ -313,10 +313,10 @@
 </t>
   </si>
   <si>
-    <t>「リソースに関するメタデータ」</t>
-  </si>
-  <si>
-    <t>リソースに関するメタデータ。これはインフラストラクチャによって維持されるコンテンツです。 コンテンツの変更は、リソースのバージョン変更と常に関連しているわけではありません。</t>
+    <t>リソースに関するMetadata</t>
+  </si>
+  <si>
+    <t>リソースに関するMetadata。これはインフラストラクチャによって維持されるコンテンツです。 コンテンツの変更は、リソースのバージョン変更と常に関連しているわけではありません。</t>
   </si>
   <si>
     <t>Resource.meta</t>
@@ -336,7 +336,7 @@
     <t>このコンテンツが作成されたルールセット</t>
   </si>
   <si>
-    <t>「リソース構築時に遵守された一連のルールを指すものであり、コンテンツを処理する際に理解する必要があります。しばしば、特別なルールを定義する実装ガイドとその他のプロファイルなどを含むものです。」</t>
+    <t>リソース構築時に遵守された一連のルールを指すものであり、コンテンツを処理する際に理解する必要があります。しばしば、特別なルールを定義する実装ガイドとその他のプロファイルなどを含むものです。</t>
   </si>
   <si>
     <t>このルールセットを主張することで、取引先の限られた集団にしか内容を理解させることができず、長期的にはデータの有用性が制限されます。しかしながら、現存するヘルスエコシステムは高度に分断化しており、一般的に計算可能な形式でデータを定義、収集、交換する準備が整っていません。できる限り、実装者および/または仕様ライターはこの要素の使用を避けるべきです。使用する場合、URLは、そのナラティブとともに他のプロファイル、値セットなどを含む実装ガイドを定義する参照となります。</t>
@@ -352,10 +352,10 @@
 </t>
   </si>
   <si>
-    <t>「リソースコンテンツの言語」(Risōsukontentsu no gengo)</t>
-  </si>
-  <si>
-    <t>「リソースが書かれている基本言語。」</t>
+    <t>「リソースコンテンツの言語」</t>
+  </si>
+  <si>
+    <t>リソースが書かれている基本言語。</t>
   </si>
   <si>
     <t>言語はインデックスとアクセシビリティをサポートするために提供されます（通常、テキスト読み上げなどのサービスは言語タグを使用します）。物語のHTML言語タグは、物語に適用されます。リソース上の言語タグは、リソース内のデータから生成される他のプレゼンテーションの言語を指定するために使用できます。すべてのコンテンツが基本言語である必要はありません。Resource.languageは自動的に物語に適用されたと想定してはいけません。言語が指定されている場合、HTMLのdiv要素にも指定する必要があります（xml：langとhtml lang属性の関係に関する情報はHTML5の規則を参照）。</t>
@@ -364,7 +364,7 @@
     <t>preferred</t>
   </si>
   <si>
-    <t>「人間の言語。」(Ningen no gengo.)</t>
+    <t>「人間の言語。」</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/languages</t>
@@ -384,10 +384,10 @@
 </t>
   </si>
   <si>
-    <t>「人間の解釈のためのリソースのテキスト要約」</t>
-  </si>
-  <si>
-    <t>「リソースの要約を含む人が読めるナビゲーションであり、リソースの内容を人に表現するために使用できます。ナビゲーションはすべての構造化されたデータをエンコードする必要はありませんが、人間がナビゲーションを読むだけで「臨床的に安全」であるために十分な詳細を含む必要があります。リソース定義には、臨床的な安全性を確保するためにナビゲーションで表現する必要があるコンテンツが定義される場合があります。」</t>
+    <t>人間の解釈のためのリソースのテキスト要約</t>
+  </si>
+  <si>
+    <t>リソースの要約を含む人が読めるナビゲーションであり、リソースの内容を人に表現するために使用できます。ナビゲーションはすべての構造化されたデータをエンコードする必要はありませんが、人間がナビゲーションを読むだけで「臨床的に安全」であるために十分な詳細を含む必要があります。リソース定義には、臨床的な安全性を確保するためにナビゲーションで表現する必要があるコンテンツが定義される場合があります。</t>
   </si>
   <si>
     <t>含まれるリソースには説明がありません。含まれないリソースには説明が必要です。場合によっては、リソースが少量のデータしか含まず、テキストだけで表現されることがあります（minOccurs = 1要素がすべて満たされている限り）。これは、情報が「テキストの塊」としてキャプチャされるレガシーシステムからのデータや、テキストが生またはナレーションされて符号化された情報が後で追加される場合に必要な場合があります。</t>
@@ -410,13 +410,13 @@
 </t>
   </si>
   <si>
-    <t>「含まれている、インラインのリソース」(Fukuma rete iru, inrain no risōsu)</t>
-  </si>
-  <si>
-    <t>「これらのリソースは、それらを含むリソースから独立した存在を持ちません。それらは独立して識別することはできず、独自の独立したトランザクション範囲を持つこともできません。」</t>
-  </si>
-  <si>
-    <t>「コンテンツが適切に識別できる場合には、これを行うべきではありません。識別が失われると、再び復元することは非常に困難であり（文脈に依存します）、メタ要素にプロファイルとタグを持つことができますが、セキュリティのラベルを持っていてはいけません。」</t>
+    <t>「含まれている、インラインのリソース」</t>
+  </si>
+  <si>
+    <t>これらのリソースは、それらを含むリソースから独立した存在を持ちません。それらは独立して識別することはできず、独自の独立したトランザクション範囲を持つこともできません。</t>
+  </si>
+  <si>
+    <t>コンテンツが適切に識別できる場合には、これを行うべきではありません。識別が失われると、再び復元することは非常に困難であり（文脈に依存します）、メタ要素にプロファイルとタグを持つことができますが、セキュリティのラベルを持っていてはいけません。</t>
   </si>
   <si>
     <t>DomainResource.contained</t>
@@ -449,7 +449,7 @@
   </si>
   <si>
     <t>ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 {hasValue() or (children().count() &gt; id.count())}
-ext-1:「拡張機能または値[x]のいずれかが必要です。両方ではありません。」 {extension.exists() != value.exists()}</t>
+ext-1:拡張機能または値[x]のいずれかが必要です。両方ではありません。 {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>MedicationAdministration.extension:requestDepartment</t>
@@ -472,7 +472,7 @@
 </t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
@@ -536,7 +536,7 @@
     <t>無視できない拡張機能 (Mushi dekinai kakuchou kinou)</t>
   </si>
   <si>
-    <t>「リソースの基本的な定義に含まれない、要素の理解や、それを含む要素の子孫の理解を修正する追加情報を表すためにも使用されることがあります。通常、修飾要素は否定や修飾を提供します。拡張機能の使用を安全で管理しやすくするために、拡張機能の定義と使用に対して厳格な統治が適用されます。実装者は拡張機能を定義することが許可されていますが、拡張機能の定義の一部として満たす必要がある要件があります。リソースを処理するアプリケーションは、修飾子拡張をチェックする必要があります。修飾子拡張は、リソースまたはドメインリソースの任意の要素の意味を変更してはなりません（修飾子拡張自体の意味も変更できません）。」</t>
+    <t>リソースの基本的な定義に含まれない、要素の理解や、それを含む要素の子孫の理解を修正する追加情報を表すためにも使用されることがあります。通常、修飾要素は否定や修飾を提供します。拡張機能の使用を安全で管理しやすくするために、拡張機能の定義と使用に対して厳格な統治が適用されます。実装者は拡張機能を定義することが許可されていますが、拡張機能の定義の一部として満たす必要がある要件があります。リソースを処理するアプリケーションは、修飾子拡張をチェックする必要があります。修飾子拡張は、リソースまたはドメインリソースの任意の要素の意味を変更してはなりません（修飾子拡張自体の意味も変更できません）。</t>
   </si>
   <si>
     <t>どのようなアプリケーション、プロジェクト、または標準が拡張機能を使用しているかに関わらず、拡張機能の使用には決して汚名が付くわけではありません - それらを使用または定義する機関または管轄区域に関係なく。拡張機能の使用こそが、FHIR仕様を誰にとっても簡単なコアレベルで維持することを可能にします。</t>
@@ -643,22 +643,22 @@
     <t>MedicationAdministration.identifier.use</t>
   </si>
   <si>
-    <t>通常|公式|温度|セカンダリ|古い（知られている場合） / usual | official | temp | secondary | old (If known)</t>
-  </si>
-  <si>
-    <t>この識別子の目的。 / The purpose of this identifier.</t>
-  </si>
-  <si>
-    <t>アプリケーションは、識別子が一時的なものであると明示的に言っていない限り、永続的であると想定できます。 / Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
-  </si>
-  <si>
-    <t>特定の使用のコンテキストが一連の識別子の中から選択される適切な識別子を許可します。 / Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
+    <t>通常|公式|一時的|セカンダリ|古い（知られている場合） / usual | official | temp | secondary | old (If known)</t>
+  </si>
+  <si>
+    <t>このidentifierの目的。 / The purpose of this identifier.</t>
+  </si>
+  <si>
+    <t>アプリケーションは、identifierが一時的なものであると明示的に言っていない限り、永続的であると想定できます。 / Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
+  </si>
+  <si>
+    <t>特定の使用のコンテキストが一連のidentifierの中から選択される適切なidentifierを許可します。 / Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
   </si>
   <si>
     <t>required</t>
   </si>
   <si>
-    <t>既知の場合、この識別子の目的を識別します。 / Identifies the purpose for this identifier, if known .</t>
+    <t>既知の場合、このidentifierの目的を識別します。 / Identifies the purpose for this identifier, if known .</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/identifier-use|4.0.1</t>
@@ -667,7 +667,7 @@
     <t>Identifier.use</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
@@ -684,22 +684,22 @@
 </t>
   </si>
   <si>
-    <t>識別子の説明 / Description of identifier</t>
-  </si>
-  <si>
-    <t>特定の目的に使用する識別子を決定するために使用できる識別子のコード化されたタイプ。 / A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
-  </si>
-  <si>
-    <t>この要素は、識別子の一般的なカテゴリのみを扱います。識別子。システムに対応するコードに使用しないでください。一部の識別子は、一般的な使用法により複数のカテゴリに分類される場合があります。システムがわかっている場合、タイプは常にシステム定義の一部であるため、タイプは不要です。ただし、システムが不明な識別子を処理する必要があることがよくあります。多くの異なるシステムが同じタイプを持っているため、タイプとシステムの間に1：1の関係はありません。 / This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
-  </si>
-  <si>
-    <t>識別子システムが不明な場合、ユーザーは識別子を使用できます。 / Allows users to make use of identifiers when the identifier system is not known.</t>
+    <t>identifierの説明 / Description of identifier</t>
+  </si>
+  <si>
+    <t>特定の目的に使用するidentifierを決定するために使用できるidentifierのコード化されたタイプ。 / A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>この要素は、identifierの一般的なカテゴリのみを扱います。identifier。システムに対応するコードに使用しないでください。一部のidentifierは、一般的な使用法により複数のカテゴリに分類される場合があります。システムがわかっている場合、タイプは常にシステム定義の一部であるため、タイプは不要です。ただし、システムが不明なidentifierを処理する必要があることがよくあります。多くの異なるシステムが同じタイプを持っているため、タイプとシステムの間に1：1の関係はありません。 / This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
+  </si>
+  <si>
+    <t>identifierシステムが不明な場合、ユーザーはidentifierを使用できます。 / Allows users to make use of identifiers when the identifier system is not known.</t>
   </si>
   <si>
     <t>extensible</t>
   </si>
   <si>
-    <t>特定の目的に使用する識別子を決定するために使用できる識別子のコード化されたタイプ。 / A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
+    <t>特定の目的に使用するidentifierを決定するために使用できるidentifierのコード化されたタイプ。 / A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
@@ -723,10 +723,10 @@
     <t>ここで付番されたIDがRp番号であることを明示するためにOID-urlとして定義された。http://jpfhir.jp/fhir/core/mhlw/IdSystem/Medication-RPGroupNumberで固定される。</t>
   </si>
   <si>
-    <t>識別子。システムは常にケースに敏感です。 / Identifier.system is always case sensitive.</t>
-  </si>
-  <si>
-    <t>識別子のセットがたくさんあります。2つの識別子を一致させるには、どのセットを扱っているかを知る必要があります。システムは、特定の一意の識別子セットを識別します。 / There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
+    <t>identifier。システムは常にケースに敏感です。 / Identifier.system is always case sensitive.</t>
+  </si>
+  <si>
+    <t>identifierのセットがたくさんあります。2つのidentifierを一致させるには、どのセットを扱っているかを知る必要があります。システムは、特定の一意のidentifierセットを識別します。 / There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
     <t>http://jpfhir.jp/fhir/core/mhlw/IdSystem/Medication-RPGroupNumber</t>
@@ -778,7 +778,7 @@
     <t>IDが使用に有効だった時間期間 / Time period when id is/was valid for use</t>
   </si>
   <si>
-    <t>識別子が使用される/有効な期間。 / Time period during which identifier is/was valid for use.</t>
+    <t>identifierが使用される/有効な期間。 / Time period during which identifier is/was valid for use.</t>
   </si>
   <si>
     <t>Identifier.period</t>
@@ -803,10 +803,10 @@
     <t>IDを発行した組織（単なるテキストである可能性があります） / Organization that issued id (may be just text)</t>
   </si>
   <si>
-    <t>識別子を発行/管理する組織。 / Organization that issued/manages the identifier.</t>
-  </si>
-  <si>
-    <t>識別子は、.reference要素を省略し、割り当て組織に関する名前またはその他のテキスト情報を反映した.display要素のみを含む場合があります。 / The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
+    <t>identifierを発行/管理する組織。 / Organization that issued/manages the identifier.</t>
+  </si>
+  <si>
+    <t>identifierは、.reference要素を省略し、割り当て組織に関する名前またはその他のテキスト情報を反映した.display要素のみを含む場合があります。 / The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
   </si>
   <si>
     <t>Identifier.assigner</t>
@@ -830,7 +830,7 @@
     <t>薬剤をオーダする単位としての処方箋に対するID。原則として投薬実施の基となったMedicationRequestのIDを設定する。</t>
   </si>
   <si>
-    <t>これはビジネス識別子であり、リソース識別子ではありません。</t>
+    <t>これはビジネスidentifierであり、リソースidentifierではありません。</t>
   </si>
   <si>
     <t>MedicationAdministration.identifier:requestIdentifier.id</t>
@@ -848,7 +848,7 @@
     <t>MedicationAdministration.identifier:requestIdentifier.system</t>
   </si>
   <si>
-    <t>識別子値の名前空間 / The namespace for the identifier value</t>
+    <t>identifier値の名前空間 / The namespace for the identifier value</t>
   </si>
   <si>
     <t>値の名前空間、つまり一意のセット値を記述するURLを確立します。 / Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
@@ -863,10 +863,10 @@
     <t>一意の値 / The value that is unique</t>
   </si>
   <si>
-    <t>通常、識別子の部分はユーザーに関連し、システムのコンテキスト内で一意のユーザーに関連しています。 / The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
-  </si>
-  <si>
-    <t>値が完全なURIの場合、システムはurn：ietf：rfc：3986でなければなりません。値の主な目的は、計算マッピングです。その結果、比較目的で正規化される可能性があります（例えば、有意でない白文字、ダッシュなどの削除）ヒューマンディスプレイ用の値は、[レンダリングされた値拡張]（拡張レンダリングValue.html）を使用して伝達できます。識別子。価値は、識別子の知識を使用しない限り、ケースに敏感なものとして扱われます。システムにより、プロセッサーは、非セイズに固有の処理が安全であると確信できます。 / If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
+    <t>通常、identifierの部分はユーザーに関連し、システムのコンテキスト内で一意のユーザーに関連しています。 / The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
+  </si>
+  <si>
+    <t>値が完全なURIの場合、システムはurn：ietf：rfc：3986でなければなりません。値の主な目的は、計算マッピングです。その結果、比較目的で正規化される可能性があります（例えば、有意でない白文字、ダッシュなどの削除）ヒューマンディスプレイ用の値は、[レンダリングされた値拡張]（拡張レンダリングValue.html）を使用して伝達できます。identifier。価値は、identifierの知識を使用しない限り、ケースに敏感なものとして扱われます。システムにより、プロセッサーは、非セイズに固有の処理が安全であると確信できます。 / If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
   </si>
   <si>
     <t>MedicationAdministration.identifier:requestIdentifier.period</t>
@@ -1031,7 +1031,7 @@
 </t>
   </si>
   <si>
-    <t>「誰が薬を受け取りましたか？」(dare ga kusuri o uketorimashita ka?)</t>
+    <t>「誰が薬を受け取りましたか？」</t>
   </si>
   <si>
     <t>薬を受け取る人、動物、またはグループ。 (Kusuri wo uketoru hito, doubutsu, matawa guruupu.)</t>
@@ -1059,7 +1059,7 @@
     <t>「エピソード・オブ・ケア」は、「エンカウンター」として提供されます。</t>
   </si>
   <si>
-    <t>「薬剤投与が行われた患者と医療提供者の間での訪問、入院、またはその他の接触。」</t>
+    <t>薬剤投与が行われた患者と医療提供者の間での訪問、入院、またはその他の接触。</t>
   </si>
   <si>
     <t>Event.context</t>
@@ -1081,7 +1081,7 @@
 </t>
   </si>
   <si>
-    <t>「管理をサポートするための追加情報」</t>
+    <t>管理をサポートするための追加情報</t>
   </si>
   <si>
     <t>薬の投与を補助する追加情報（例えば、患者の身長や体重）。</t>
@@ -1097,10 +1097,10 @@
 Period</t>
   </si>
   <si>
-    <t>「管理の開始時刻と終了時刻」(Kanri no kaishi jikoku to shūryō jikoku)</t>
-  </si>
-  <si>
-    <t>「与えられた属性が「真実」となっている場合に、行政が行われた（または行われなかった）特定の日時または時間の間隔。錠剤の服用など、多くの行政では、dateTimeの使用が適切です。」</t>
+    <t>「管理の開始時刻と終了時刻」</t>
+  </si>
+  <si>
+    <t>与えられた属性が「真実」となっている場合に、行政が行われた（または行われなかった）特定の日時または時間の間隔。錠剤の服用など、多くの行政では、dateTimeの使用が適切です。</t>
   </si>
   <si>
     <t>Event.occurrence[x]</t>
@@ -1122,10 +1122,10 @@
 </t>
   </si>
   <si>
-    <t>「薬剤投与を行ったのは誰で、何をしたのか？」</t>
-  </si>
-  <si>
-    <t>「薬の投与を行った人や物、および彼らがどのように関与したかを示す。」</t>
+    <t>薬剤投与を行ったのは誰で、何をしたのか？</t>
+  </si>
+  <si>
+    <t>薬の投与を行った人や物、および彼らがどのように関与したかを示す。</t>
   </si>
   <si>
     <t>Event.performer</t>
@@ -1155,7 +1155,7 @@
     <t>実装によって定義される追加コンテンツ</t>
   </si>
   <si>
-    <t>「要素の基本的な定義に含まれない追加情報を表すために使用されることがあります。拡張機能の使用を安全かつ管理しやすくするために、定義および使用に適用される厳格なガバナンスのセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たす必要のある要件のセットがあります。」</t>
+    <t>要素の基本的な定義に含まれない追加情報を表すために使用されることがあります。拡張機能の使用を安全かつ管理しやすくするために、定義および使用に適用される厳格なガバナンスのセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たす必要のある要件のセットがあります。</t>
   </si>
   <si>
     <t>MedicationAdministration.performer.modifierExtension</t>
@@ -1165,11 +1165,11 @@
 user contentmodifiers</t>
   </si>
   <si>
-    <t>「認識されなくても無視できない拡張機能」(Ninshiki sarenakutemo mushi dekinai kakuchou kinou)</t>
-  </si>
-  <si>
-    <t>「基本的な要素の定義に含まれない追加情報を表すために使用されることがあり、それによって、その要素自体または取り込んでいる要素の子孫の理解を修正する。修飾子要素は通常、否定または修飾を提供します。拡張機能の安全で管理しやすい使用を実現するために、定義および使用に厳しいガバナンスセットが適用されています。どの実装者でも拡張機能を定義できますが、拡張機能の定義の一部として満たす必要がある要件があります。リソースを処理するアプリケーションは、修飾子拡張子をチェックする必要があります。
-修飾子拡張機能は、リソースまたはドメインリソースの任意の要素の意味を変更してはなりません（修飾子拡張自体の意味を変更することもできません）。」</t>
+    <t>認識されなくても無視できない拡張機能</t>
+  </si>
+  <si>
+    <t>基本的な要素の定義に含まれない追加情報を表すために使用されることがあり、それによって、その要素自体または取り込んでいる要素の子孫の理解を修正する。修飾子要素は通常、否定または修飾を提供します。拡張機能の安全で管理しやすい使用を実現するために、定義および使用に厳しいガバナンスセットが適用されています。どの実装者でも拡張機能を定義できますが、拡張機能の定義の一部として満たす必要がある要件があります。リソースを処理するアプリケーションは、修飾子拡張子をチェックする必要があります。
+修飾子拡張機能は、リソースまたはドメインリソースの任意の要素の意味を変更してはなりません（修飾子拡張自体の意味を変更することもできません）。</t>
   </si>
   <si>
     <t>BackboneElement.modifierExtension</t>
@@ -1178,13 +1178,13 @@
     <t>MedicationAdministration.performer.function</t>
   </si>
   <si>
-    <t>「パフォーマンスの種類」(Pafōmansu no shurui)</t>
+    <t>「パフォーマンスの種類」</t>
   </si>
   <si>
     <t>演者の医薬品投与における関与タイプを区別します。 (Ensha no iyakuhin tōyo ni okeru kan'yo taipu o kubetsushimasu.)</t>
   </si>
   <si>
-    <t>「薬物管理を行った個人の役割を説明するコード」</t>
+    <t>薬物管理を行った個人の役割を説明するコード</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/med-admin-perform-function</t>
@@ -1203,10 +1203,10 @@
 </t>
   </si>
   <si>
-    <t>「薬剤投与を行ったのは誰ですか？」(Yakuzaiteiyogyou o okonatta no wa dare desu ka?)</t>
-  </si>
-  <si>
-    <t>「薬剤投与を行った人物または物品を示す」</t>
+    <t>「薬剤投与を行ったのは誰ですか？」</t>
+  </si>
+  <si>
+    <t>薬剤投与を行った人物または物品を示す</t>
   </si>
   <si>
     <t>Event.performer.actor</t>
@@ -1224,7 +1224,7 @@
     <t>与えられた薬を説明するコード。</t>
   </si>
   <si>
-    <t>「薬剤投与が行われた理由を示すコードのセット。」</t>
+    <t>薬剤投与が行われた理由を示すコードのセット。</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/reason-medication-given-codes</t>
@@ -1246,13 +1246,13 @@
 </t>
   </si>
   <si>
-    <t>「薬が投与された理由を支持する状態または観察」</t>
+    <t>薬が投与された理由を支持する状態または観察</t>
   </si>
   <si>
     <t>薬剤が投与された理由を支持する状態または観察。</t>
   </si>
   <si>
-    <t>「これは、薬剤依頼の理由となる状態に関する参照です。もしコードしか存在しない場合は、reasonCodeを使用してください。」</t>
+    <t>これは、薬剤依頼の理由となる状態に関する参照です。もしコードしか存在しない場合は、reasonCodeを使用してください。</t>
   </si>
   <si>
     <t>Event.reasonReference</t>
@@ -1277,10 +1277,10 @@
     <t>"リクエスト管理対象として実行してください。" (Rikuesuto kanri taishou toshite jikkou shite kudasai.)</t>
   </si>
   <si>
-    <t>「管理を実行するための元の要求、指示、または権限。」</t>
-  </si>
-  <si>
-    <t>「これは、意図がオーダーまたはインスタンスオーダーであるMedicationRequestへの参照であり、意図が他の値であるMedicationRequestへの参照ではありません。」</t>
+    <t>管理を実行するための元の要求、指示、または権限。</t>
+  </si>
+  <si>
+    <t>これは、意図がオーダーまたはインスタンスオーダーであるMedicationRequestへの参照であり、意図が他の値であるMedicationRequestへの参照ではありません。</t>
   </si>
   <si>
     <t>Event.basedOn</t>
@@ -1299,7 +1299,7 @@
 </t>
   </si>
   <si>
-    <t>「投与するための装置」(touyo suru tame no souchi)</t>
+    <t>投与するための装置</t>
   </si>
   <si>
     <t>患者に薬剤を投与するのに使われる装置。例えば、特定の注入ポンプ。</t>
@@ -1318,10 +1318,10 @@
 </t>
   </si>
   <si>
-    <t>「行政に関する情報」(Gyōsei ni kansuru jōhō)</t>
-  </si>
-  <si>
-    <t>「他の属性では伝えられない薬剤投与に関する追加情報」</t>
+    <t>「行政に関する情報」</t>
+  </si>
+  <si>
+    <t>他の属性では伝えられない薬剤投与に関する追加情報</t>
   </si>
   <si>
     <t>Event.note</t>
@@ -1371,16 +1371,16 @@
     <t>MedicationAdministration.dosage.site</t>
   </si>
   <si>
-    <t>「投与された体の部位」(Touyo sareta karada no bubui)</t>
+    <t>投与された体の部位</t>
   </si>
   <si>
     <t>薬剤が最初に体内に入った解剖学的な部位の符号化された規格。例えば、「左腕」。</t>
   </si>
   <si>
-    <t>「もし使用用途がBodySiteリソースから属性を必要とする場合（例えば、個別に識別および追跡するため）は、標準の拡張子[bodySite]（extension-bodysite.html）を使用してください。要約コードであるか、非常に正確な位置の定義への参照であるか、双方である可能性があります。」</t>
-  </si>
-  <si>
-    <t>「薬剤が体内に入るか、体表面に塗布される場所を示すコード化された概念。」</t>
+    <t>もし使用用途がBodySiteリソースから属性を必要とする場合（例えば、個別に識別および追跡するため）は、標準の拡張子[bodySite]（extension-bodysite.html）を使用してください。要約コードであるか、非常に正確な位置の定義への参照であるか、双方である可能性があります。</t>
+  </si>
+  <si>
+    <t>薬剤が体内に入るか、体表面に塗布される場所を示すコード化された概念。</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/approach-site-codes</t>
@@ -1401,7 +1401,7 @@
     <t>治療剤の患者への内部または表面への投与のルートまたは生理学的経路を指定するコード。例えば、表面的な投与、静注など。</t>
   </si>
   <si>
-    <t>「治療薬剤を被験者の体内あるいは体表面へ投与する生理学的ルートや経路を記述する符号化された概念」</t>
+    <t>治療薬剤を被験者の体内あるいは体表面へ投与する生理学的ルートや経路を記述する符号化された概念</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/route-codes</t>
@@ -1416,7 +1416,7 @@
     <t>MedicationAdministration.dosage.method</t>
   </si>
   <si>
-    <t>「薬剤がどのように投与されたか」</t>
+    <t>薬剤がどのように投与されたか</t>
   </si>
   <si>
     <t>薬剤が体内または体表に導入される方法を示すコード化された値。 この属性は通常、非Populatedでありません。 通常、注射に使用されます。 たとえば、スロープッシュ、深いIV。</t>
@@ -1425,7 +1425,7 @@
     <t>この属性があまり使用されていない理由の一つに、方法がしばしば経路や投与形態と事前調整されていることが挙げられる。これは、経路コードまたは投与形態コードで方法が事前に調整される場合があることを意味する。また、経路コードや投与形態コードに使用されるコーディングシステムを決定する実装に関する決定は、どの程度の頻度でメソッドコードが追加されるかを決定する。たとえば、経路コードや投与形態コードが方法コードを事前調整する場合、この属性はあまり追加されないかもしれない。事前調整が行われていない場合、方法コードが頻繁に使用される可能性がある。</t>
   </si>
   <si>
-    <t>「薬剤が投与される方法を記述する暗号化された概念。」</t>
+    <t>薬剤が投与される方法を記述する暗号化された概念。</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/administration-method-codes</t>
@@ -1450,7 +1450,7 @@
     <t>一回の投与イベントで与えられる薬剤の量。この値は、錠剤を飲んだり注射をしたりするような、本質的に瞬時のイベントである場合に使用します。</t>
   </si>
   <si>
-    <t>「もし投与速度が即時でない場合、単回の投与期間中に投与される総量を示すことができます。」</t>
+    <t>もし投与速度が即時でない場合、単回の投与期間中に投与される総量を示すことができます。</t>
   </si>
   <si>
     <t>.doseQuantity</t>
@@ -1466,7 +1466,7 @@
 Quantity {SimpleQuantity}</t>
   </si>
   <si>
-    <t>「時間当たりの投与量」</t>
+    <t>時間当たりの投与量</t>
   </si>
   <si>
     <t>患者に投与されたあるいは投与される薬剤の導入速度を特定します。通常、投与速度は、100 ml / 1時間、または100 ml /時間（時間あたり100 ml）のような輸液の速度として表されます。時間単位あたりの速度として表される場合もあります。例えば、500 ml / 2時間のように。その他の例：200 mcg /分あるいは1分間当たり200 mcg；1リットル/8時間。</t>
@@ -1488,10 +1488,10 @@
 </t>
   </si>
   <si>
-    <t>「ライフサイクルで興味深いイベントのリスト」</t>
-  </si>
-  <si>
-    <t>「行政が検証された時などに起こった興味深い出来事の要約」</t>
+    <t>ライフサイクルで興味深いイベントのリスト</t>
+  </si>
+  <si>
+    <t>行政が検証された時などに起こった興味深い出来事の要約</t>
   </si>
   <si>
     <t>この要請のすべてのバージョンの起源が含まれているわけではない可能性があります。ただし、「関連性」または重要と見なされるものに限定されます。それに含まれる証跡には、このリソースの現在のバージョンに関連するものは含まれません。 （そのプロバイナンスが「関連性のある」変更である場合、後の更新の一部として追加する必要があります。その時までは、このバージョンを指すプロバイナンスとして直接クエリできます。All Provenancesは、この要求の過去のバージョンを主題として持つ必要があります。</t>
@@ -1828,7 +1828,7 @@
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="145.265625" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="155.12109375" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="58.77734375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
